--- a/outputs/OOP_Corridor_Daily_Operations_Addendum_20260825.xlsx
+++ b/outputs/OOP_Corridor_Daily_Operations_Addendum_20260825.xlsx
@@ -965,7 +965,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tuesday 25 august</t>
+          <t>Tuesday 25 August</t>
         </is>
       </c>
     </row>
